--- a/Каталог фотографий сетей.xlsx
+++ b/Каталог фотографий сетей.xlsx
@@ -45,8 +45,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:I36"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="42" customWidth="1"/>
@@ -858,6 +858,899 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Alidi.jpg</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Фотки переговоров/Alidi.jpg</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ALIDI</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>HoReCa; оптовый дистрибьютор; Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Бакалея; Крупы; Свежие продукты; Охлажденные товары; Замороженные товары; Напитки; HoReCa; Food</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Средний; Средний+</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2 - близкий по каналу/сегменту</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>На табличке указаны HoReCa, бакалея dry, fresh, охлажденные, замороженные товары и напитки</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Baza.jpg</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Фотки переговоров/Baza.jpg</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BAZA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Региональная food-сеть; Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Бакалея; Крупы; Свежие продукты; Охлажденные товары; Замороженные товары; ЗОЖ; ЭКО; Напитки; Food</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Средний; Средний+</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2 - близкий по каналу/сегменту</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>На табличке указаны бакалея dry, fresh, охлажденные, замороженные товары, ЗОЖ/ЭКО и напитки</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>coffeebon.jpg</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Фотки переговоров/coffeebon.jpg</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>COFFEEBON</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>HoReCa; кофейни/кафе; Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Бакалея; Кофе; Напитки; HoReCa; Food</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Средний; Средний+</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2 - близкий по каналу/сегменту</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Подходит для кофе, напитков, бакалеи и HoReCa-кейсов</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Gustus.jpg</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Фотки переговоров/Gustus.jpg</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>GUSTUS</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Региональная food-сеть; Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Бакалея; Крупы; Свежие продукты; Охлажденные товары; Замороженные товары; ЭКО; ЗОЖ; Напитки; Food</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Средний; Средний+</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2 - близкий по каналу/сегменту</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>На табличке указаны бакалея dry, fresh, охлажденные, замороженные товары, ЭКО/ЗОЖ продукты и напитки</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Horeca-snab.jpg</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Фотки переговоров/Horeca-snab.jpg</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>HoReCa-snab</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>HoReCa; специализированный поставщик; Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Бакалея; Свежие продукты; Охлажденные товары; Замороженные товары; ЭКО; ЗОЖ; Напитки; HoReCa; Food</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Средний; Средний+</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2 - близкий по каналу/сегменту</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>На табличке указаны бакалея dry, fresh, охлажденные, замороженные товары, ЭКО/ЗОЖ продукты и напитки</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Millstream Питер бакалея фреш охлажденка напистки алкоголь.jpg</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Фотки переговоров/Millstream Питер бакалея фреш охлажденка напистки алкоголь.jpg</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Millstream</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Региональная food-сеть; Санкт-Петербург; напитки/алкоголь</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Бакалея; Крупы; Свежие продукты; Охлажденные товары; Напитки; Алкоголь; Food</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Средний; Средний+</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2 - близкий по каналу/сегменту</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Атрибуты взяты из имени файла; в имени есть опечатка "напистки"</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Prodly.jpg</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Фотки переговоров/Prodly.jpg</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Prodly</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Требует проверки; визуально на фото табличка S2B</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Бакалея; Свежие продукты; Охлажденные товары; ЭКО; ЗОЖ; Напитки; Алкоголь; Non-food; Food</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Средний; Средний+</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>4 - универсальный fallback</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Файл называется Prodly, но визуально кадр совпадает с S2B/на табличке S2B; нужно проверить название сети</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>S2B.jpg</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Фотки переговоров/S2B.jpg</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>S2B</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>HoReCa; специализированный канал; Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Бакалея; Свежие продукты; Охлажденные товары; ЭКО; ЗОЖ; Напитки; Алкоголь; Non-food; Food</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Средний; Средний+</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2 - близкий по каналу/сегменту</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>На табличке указаны бакалея, fresh, охлажденные товары, ЭКО/ЗОЖ, напитки, алкоголь и nonfood</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Аврора Питер Бакалея.jpg</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Фотки переговоров/Аврора Питер Бакалея.jpg</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Аврора</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Региональная сеть; Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Бакалея; Крупы; Food</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Эконом; Средний</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2 - близкий по каналу/сегменту</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Атрибуты взяты из имени файла: Санкт-Петербург, бакалея</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Бомонд Питер бакалея напитки.jpg</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Фотки переговоров/Бомонд Питер бакалея напитки.jpg</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Бомонд</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Региональная сеть; Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Бакалея; Крупы; Напитки; Food</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Средний; Средний+</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2 - близкий по каналу/сегменту</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Атрибуты взяты из имени файла: Санкт-Петербург, бакалея и напитки</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Колхоз Питер бакалея фреш охлажденка заморозка напитки nonfood.jpg</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Фотки переговоров/Колхоз Питер бакалея фреш охлажденка заморозка напитки nonfood.jpg</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Колхоз</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Региональная food-сеть; Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Бакалея; Крупы; Свежие продукты; Охлажденные товары; Замороженные товары; Напитки; Non-food; Food</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2 - близкий по каналу/сегменту</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Атрибуты взяты из имени файла: широкий food-ассортимент плюс nonfood</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Магнит СЗФО Питер Food.jpg</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Фотки переговоров/Магнит СЗФО Питер Food.jpg</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Магнит СЗФО</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Федеральная сеть; СЗФО; Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Крупы; Мясные деликатесы; Овощная консервация; Молочная продукция Сыры; Food</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Эконом; Средний</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>3 - универсальный сетевой пример</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Региональный кадр федеральной сети Магнит для СЗФО/Санкт-Петербурга</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Почта России бакалея напитки nonfood.jpg</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Фотки переговоров/Почта России бакалея напитки nonfood.jpg</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Почта России</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Федеральная сеть; отделения/ритейл; convenience</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Бакалея; Крупы; Напитки; Non-food; Товары импульсного спроса</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Эконом; Средний</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>3 - универсальный сетевой пример</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Атрибуты взяты из имени файла: бакалея, напитки и nonfood</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Пуд Симферополь бакалея ЭКО ЗОЖ Напитки nonfood.jpg</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Фотки переговоров/Пуд Симферополь бакалея ЭКО ЗОЖ Напитки nonfood.jpg</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ПУД</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Региональная сеть; Симферополь; Крым</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Бакалея; Крупы; ЭКО; ЗОЖ; Напитки; Non-food; Food</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Эконом; Средний</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2 - близкий по каналу/сегменту</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Атрибуты взяты из имени файла: Симферополь, бакалея, ЭКО/ЗОЖ, напитки и nonfood</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Светофор Питер бакалея фреш охлажденка заморозка ЭКО напитки.jpg</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Фотки переговоров/Светофор Питер бакалея фреш охлажденка заморозка ЭКО напитки.jpg</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Светофор</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Федеральная сеть; дискаунтер; Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Бакалея; Крупы; Свежие продукты; Охлажденные товары; Замороженные товары; ЭКО; Напитки; Food</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Эконом</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>3 - универсальный сетевой пример</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Атрибуты взяты из имени файла; сильный пример дискаунтера для массового food</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Сигма Лэнд ДНР Донецк  все группы СТМ.jpg</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Фотки переговоров/Сигма Лэнд ДНР Донецк  все группы СТМ.jpg</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Сигма Лэнд</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Региональная сеть; Донецк; ДНР; СТМ</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Крупы; Мясные деликатесы; Овощная консервация; Молочная продукция Сыры; Бакалея; Свежие продукты; Замороженные товары; Напитки; Non-food; СТМ; Food</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Эконом; Средний</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>3 - универсальный сетевой пример</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Атрибуты взяты из имени файла: все группы и СТМ</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Сити Гурме  Мурманск бакалея фреш охлажденка заморозка ЭКО ЗОЖ Напитки алкоголь.jpg</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Фотки переговоров/Сити Гурме  Мурманск бакалея фреш охлажденка заморозка ЭКО ЗОЖ Напитки алкоголь.jpg</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Сити Гурме</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Региональная food-сеть; Мурманск; premium/convenience</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Бакалея; Крупы; Свежие продукты; Охлажденные товары; Замороженные товары; ЭКО; ЗОЖ; Напитки; Алкоголь; Food</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Средний+; Премиум</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2 - близкий по каналу/сегменту</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Атрибуты взяты из имени файла: Мурманск, широкий food-ассортимент, ЭКО/ЗОЖ, напитки и алкоголь</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Универсам Вместе бакалея фреш охлажденка заморозка ЭКО ЗОЖ напитки алкоголь.jpg</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Фотки переговоров/Универсам Вместе бакалея фреш охлажденка заморозка ЭКО ЗОЖ напитки алкоголь.jpg</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Универсам Вместе</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Региональная food-сеть; универсам</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Бакалея; Крупы; Свежие продукты; Охлажденные товары; Замороженные товары; ЭКО; ЗОЖ; Напитки; Алкоголь; Food</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2 - близкий по каналу/сегменту</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Атрибуты взяты из имени файла: широкий food-ассортимент, ЭКО/ЗОЖ, напитки и алкоголь</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Фунт Псков бакалея, фреш охлажденка заморозка ЗОЖ ЭКО Напитки.jpg</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Фотки переговоров/Фунт Псков бакалея, фреш охлажденка заморозка ЗОЖ ЭКО Напитки.jpg</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Фунт</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Региональная food-сеть; Псков</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Бакалея; Крупы; Свежие продукты; Охлажденные товары; Замороженные товары; ЗОЖ; ЭКО; Напитки; Food</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Эконом; Средний</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2 - близкий по каналу/сегменту</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Атрибуты взяты из имени файла: Псков, широкий food-ассортимент, ЗОЖ/ЭКО и напитки</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I17"/>
 </worksheet>

--- a/Каталог фотографий сетей.xlsx
+++ b/Каталог фотографий сетей.xlsx
@@ -11,7 +11,6 @@
     <sheet name="Лист2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="125725"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -1873,7 +1872,7 @@
     <col min="4" max="4" width="130.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="33">
+    <row r="1" spans="1:4" ht="16.5">
       <c r="A1" s="3" t="s">
         <v>111</v>
       </c>
@@ -2013,7 +2012,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="49.5">
+    <row r="11" spans="1:4" ht="33">
       <c r="A11" s="3" t="s">
         <v>125</v>
       </c>
